--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N112_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N112_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.24017072817293</v>
+        <v>9.464027743328101</v>
       </c>
       <c r="D2" t="n">
-        <v>58.48386275786371</v>
+        <v>9.503627698152853</v>
       </c>
       <c r="E2" t="n">
-        <v>14.7191945245669</v>
+        <v>2.391869110242121</v>
       </c>
       <c r="F2" t="n">
-        <v>15.14060293217438</v>
+        <v>2.460347976478337</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>50.53319765756866</v>
+        <v>8.211644619354907</v>
       </c>
       <c r="D3" t="n">
-        <v>50.84418863640739</v>
+        <v>8.2621806534162</v>
       </c>
       <c r="E3" t="n">
-        <v>14.7191945245669</v>
+        <v>2.391869110242121</v>
       </c>
       <c r="F3" t="n">
-        <v>15.14060293217438</v>
+        <v>2.460347976478337</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.99016015258147</v>
+        <v>2.110901024794488</v>
       </c>
       <c r="D4" t="n">
-        <v>14.23190759798387</v>
+        <v>2.312684984672379</v>
       </c>
       <c r="E4" t="n">
-        <v>14.7191945245669</v>
+        <v>2.391869110242121</v>
       </c>
       <c r="F4" t="n">
-        <v>15.14060293217438</v>
+        <v>2.460347976478337</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.55757686676424</v>
+        <v>2.690606240849188</v>
       </c>
       <c r="D5" t="n">
-        <v>18.21726166164881</v>
+        <v>2.960305020017932</v>
       </c>
       <c r="E5" t="n">
-        <v>14.7191945245669</v>
+        <v>2.391869110242121</v>
       </c>
       <c r="F5" t="n">
-        <v>15.14060293217438</v>
+        <v>2.460347976478337</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.34016088740551</v>
+        <v>3.305276144203396</v>
       </c>
       <c r="D6" t="n">
-        <v>21.19664380272079</v>
+        <v>3.444454617942128</v>
       </c>
       <c r="E6" t="n">
-        <v>14.7191945245669</v>
+        <v>2.391869110242121</v>
       </c>
       <c r="F6" t="n">
-        <v>15.14060293217438</v>
+        <v>2.460347976478337</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.38787793812806</v>
+        <v>3.47553016494581</v>
       </c>
       <c r="D7" t="n">
-        <v>21.07609100569648</v>
+        <v>3.424864788425678</v>
       </c>
       <c r="E7" t="n">
-        <v>14.7191945245669</v>
+        <v>2.391869110242121</v>
       </c>
       <c r="F7" t="n">
-        <v>15.14060293217438</v>
+        <v>2.460347976478337</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.734410440947367</v>
+        <v>0.9318416966539472</v>
       </c>
       <c r="D8" t="n">
-        <v>8.950505398994968</v>
+        <v>1.454457127336682</v>
       </c>
       <c r="E8" t="n">
-        <v>14.7191945245669</v>
+        <v>2.391869110242121</v>
       </c>
       <c r="F8" t="n">
-        <v>15.14060293217438</v>
+        <v>2.460347976478337</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.02305573418963</v>
+        <v>2.766246556805815</v>
       </c>
       <c r="D9" t="n">
-        <v>13.04293252642552</v>
+        <v>2.119476535544148</v>
       </c>
       <c r="E9" t="n">
-        <v>14.7191945245669</v>
+        <v>2.391869110242121</v>
       </c>
       <c r="F9" t="n">
-        <v>15.14060293217438</v>
+        <v>2.460347976478337</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.97790575571199</v>
+        <v>4.058909685303199</v>
       </c>
       <c r="D10" t="n">
-        <v>21.03381615927605</v>
+        <v>3.417995125882358</v>
       </c>
       <c r="E10" t="n">
-        <v>14.7191945245669</v>
+        <v>2.391869110242121</v>
       </c>
       <c r="F10" t="n">
-        <v>15.14060293217438</v>
+        <v>2.460347976478337</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.82776024343029</v>
+        <v>5.172011039557423</v>
       </c>
       <c r="D11" t="n">
-        <v>29.11473945073115</v>
+        <v>4.731145160743813</v>
       </c>
       <c r="E11" t="n">
-        <v>14.7191945245669</v>
+        <v>2.391869110242121</v>
       </c>
       <c r="F11" t="n">
-        <v>15.14060293217438</v>
+        <v>2.460347976478337</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>15.77945984300491</v>
+        <v>2.564162224488298</v>
       </c>
       <c r="D12" t="n">
-        <v>16.18927989428536</v>
+        <v>2.630757982821371</v>
       </c>
       <c r="E12" t="n">
-        <v>14.7191945245669</v>
+        <v>2.391869110242121</v>
       </c>
       <c r="F12" t="n">
-        <v>15.14060293217438</v>
+        <v>2.460347976478337</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>29.98826706240197</v>
+        <v>4.873093397640321</v>
       </c>
       <c r="D13" t="n">
-        <v>5.70087712549569</v>
+        <v>0.9263925328930496</v>
       </c>
       <c r="E13" t="n">
-        <v>14.7191945245669</v>
+        <v>2.391869110242121</v>
       </c>
       <c r="F13" t="n">
-        <v>15.14060293217438</v>
+        <v>2.460347976478337</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>40.90331948180236</v>
+        <v>6.646789415792885</v>
       </c>
       <c r="D14" t="n">
-        <v>36.16973873281365</v>
+        <v>5.877582544082218</v>
       </c>
       <c r="E14" t="n">
-        <v>14.7191945245669</v>
+        <v>2.391869110242121</v>
       </c>
       <c r="F14" t="n">
-        <v>15.14060293217438</v>
+        <v>2.460347976478337</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
